--- a/labs/sql-ltr-backup-migration/cost-model/ltr-backup-storage-costs.xlsx
+++ b/labs/sql-ltr-backup-migration/cost-model/ltr-backup-storage-costs.xlsx
@@ -704,10 +704,10 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="39" customHeight="1">
+    <row r="27" ht="104" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED: the compression ratio. This is the weakest input and it drives the largest term. Measured ratios in testing ranged from 1.02x on incompressible data to 33x on highly repetitive data, against a default assumption of 4x. Budget with the worst ratio you actually observe.</t>
+          <t>MEASURED (2026-09-10): the compression ratio. Ratios were measured on live Azure SQL databases via sqlpackage over a private endpoint (Standard_D4s_v5, same-region, swedencentral). Mixed realistic business data: 3.98x-4.25x (validates the 4.0x default). Incompressible floor (random bytes): 1.04x. A synthetic upper bound of 145x was also observed from a single-repeated-byte seed; it is not a planning value. The remaining uncertainty is which shape the reader's data resembles: budget with 1.04x (worst case, largest artifacts) and note that mixed realistic data lands near 4x. If your databases are encrypted or pre-compressed at the application layer, use the 1.04x row.</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Source GB per artifact GB. THE weakest assumption. Measured 1.02x to 33x.</t>
+          <t>Source GB per artifact GB. Measured 2026-09-10: 3.98-4.25x on mixed realistic data (validates this default). Incompressible floor: 1.04x. Budget with 1.04x if you do not know your data shape. See 'Compression sensitivity' for the full range.</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3982,7 +3982,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="B6" s="38">
         <f>Parameters!$B$19/$A6</f>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>Measured worst case: already-compressed or encrypted data.</t>
+          <t>MEASURED incompressible floor (2026-09-10): random/high-entropy data such as encrypted blobs or compressed application payloads. Recommended budgeting input when data shape is unknown.</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>Pessimistic.</t>
+          <t>Pessimistic estimate.</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Default assumption in the toolkit. Unverified.</t>
+          <t>MEASURED for mixed realistic data (2026-09-10): range 3.98-4.25x across 1, 5 and 20 GB databases. Validated default. Use this if your databases hold typical structured business data.</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>Optimistic; text-heavy schemas.</t>
+          <t>Optimistic; text-heavy schemas with low cardinality.</t>
         </is>
       </c>
     </row>
@@ -4130,56 +4130,34 @@
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>Very repetitive data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B13" s="36">
-        <f>Parameters!$B$19/$A13</f>
-        <v/>
-      </c>
-      <c r="C13" s="29">
-        <f>$B13*Parameters!$B$14*Parameters!$B$7</f>
-        <v/>
-      </c>
-      <c r="D13" s="29">
-        <f>$C13+$B13*Parameters!$B$16+ROUNDUP($B13*1024/Parameters!$B$11,0)/10000*Parameters!$B$15</f>
-        <v/>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>Measured best case: highly repetitive test data. Do not plan on this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+          <t>Very repetitive data; unlikely in production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Worst case vs default assumption:</t>
         </is>
       </c>
-      <c r="D15" s="42">
+      <c r="D14" s="42">
         <f>IFERROR($D6/$D10,0)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Yellow is the toolkit default. Orange is the measured worst case. The gap between them is the single largest source of error in this model.</t>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Yellow is the measured default (4.0x, validated for mixed realistic data on 2026-09-10). Orange is the measured incompressible floor (1.04x, random/high-entropy data). The ratio between them is the planning uncertainty: it is no longer a guess about the ratio itself, but about which data shape your databases resemble.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A14:C14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
